--- a/AutoRegularInspection/外观检查.xlsx
+++ b/AutoRegularInspection/外观检查.xlsx
@@ -4,19 +4,32 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18525" windowHeight="6480"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="桥面系" sheetId="1" r:id="rId1"/>
     <sheet name="上部结构" sheetId="2" r:id="rId2"/>
     <sheet name="下部结构" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="163">
   <si>
     <t>序号</t>
   </si>
@@ -60,6 +73,9 @@
     <t>单位2数量</t>
   </si>
   <si>
+    <t>缺损百分比</t>
+  </si>
+  <si>
     <t>使用自定义单位</t>
   </si>
   <si>
@@ -94,6 +110,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>0#</t>
     </r>
     <r>
@@ -163,6 +184,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>3#</t>
     </r>
     <r>
@@ -276,6 +302,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>主梁翼板及腹板外侧大面积水蚀，面积约占主梁翼板总面积</t>
     </r>
     <r>
@@ -298,6 +329,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>主梁</t>
     </r>
     <r>
@@ -490,6 +526,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>0-1#</t>
     </r>
     <r>
@@ -512,6 +553,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>0-2#</t>
     </r>
     <r>
@@ -537,6 +583,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>1-1#</t>
     </r>
     <r>
@@ -559,6 +610,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>1-2#</t>
     </r>
     <r>
@@ -584,6 +640,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>2-1#</t>
     </r>
     <r>
@@ -606,6 +667,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>2-2#</t>
     </r>
     <r>
@@ -631,6 +697,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>3-1#</t>
     </r>
     <r>
@@ -653,6 +724,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>3-2#</t>
     </r>
     <r>
@@ -678,6 +754,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>3#</t>
     </r>
     <r>
@@ -699,7 +780,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -725,34 +806,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -766,14 +819,6 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -813,6 +858,21 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -863,7 +923,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -878,55 +959,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -944,31 +983,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -992,6 +1019,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1004,7 +1043,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1028,7 +1091,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1052,6 +1127,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1069,21 +1150,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1116,6 +1182,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1172,148 +1253,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1323,52 +1404,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1639,14 +1720,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="4" max="5" width="22.1428571428571" customWidth="1"/>
     <col min="7" max="7" width="36.7142857142857" customWidth="1"/>
+    <col min="12" max="12" width="11.2857142857143" customWidth="1"/>
+    <col min="14" max="14" width="11.2857142857143" customWidth="1"/>
+    <col min="15" max="15" width="12.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1689,339 +1773,366 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2">
         <v>2</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N2">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L3">
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L4">
         <v>12</v>
       </c>
       <c r="M4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L5">
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s">
         <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" t="s">
-        <v>35</v>
       </c>
       <c r="L6">
         <v>7</v>
       </c>
       <c r="M6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7" t="s">
-        <v>21</v>
-      </c>
       <c r="N7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8" t="s">
-        <v>21</v>
-      </c>
       <c r="N8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N9">
         <v>0</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2034,7 +2145,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="4" max="5" width="13.4285714285714" customWidth="1"/>
@@ -2042,7 +2153,7 @@
     <col min="7" max="7" width="22.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2050,7 +2161,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -2085,828 +2196,891 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L3">
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L4">
         <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L7">
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8">
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L9">
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E12" s="1">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L12">
         <v>38</v>
       </c>
       <c r="M12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E13">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N13">
         <v>0.0025</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E14">
         <v>10</v>
       </c>
       <c r="F14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14" t="s">
+        <v>98</v>
+      </c>
+      <c r="H14" t="s">
+        <v>99</v>
+      </c>
+      <c r="J14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" t="s">
+        <v>30</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14" t="s">
         <v>96</v>
-      </c>
-      <c r="G14" t="s">
-        <v>97</v>
-      </c>
-      <c r="H14" t="s">
-        <v>98</v>
-      </c>
-      <c r="J14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" t="s">
-        <v>29</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14" t="s">
-        <v>95</v>
       </c>
       <c r="N14">
         <v>0.015</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E15" s="1">
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L15">
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N15">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E16">
         <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L16">
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N16">
         <v>0.004</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E17">
         <v>13</v>
       </c>
       <c r="F17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L17">
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N17">
         <v>0.0025</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E18" s="1">
         <v>14</v>
       </c>
       <c r="F18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L18">
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N18">
         <v>0.0024</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E19">
         <v>15</v>
       </c>
       <c r="F19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L19">
         <v>1</v>
       </c>
       <c r="M19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N19">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E20">
         <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E21" s="1">
         <v>17</v>
       </c>
       <c r="F21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N21">
         <v>0</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2918,7 +3092,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="11.1428571428571" customWidth="1"/>
@@ -2926,7 +3100,7 @@
     <col min="6" max="6" width="26.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2934,7 +3108,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -2969,377 +3143,407 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L3">
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L4">
         <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L5">
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L6">
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L7">
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L8">
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L9">
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N10">
         <v>0</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
